--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260727.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>399,205,735</t>
+          <t>29,658,404</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>29,658,404</t>
+          <t>399,205,735</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8,286,796</t>
+          <t>7,201,573</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7,201,573</t>
+          <t>8,286,796</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>294,744,952</t>
+          <t>15,172,713</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,172,713</t>
+          <t>294,744,952</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>69,545,541</t>
+          <t>25,646,935</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>25,646,935</t>
+          <t>69,545,541</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>111,087,535</t>
+          <t>4,019,061</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>4,019,061</t>
+          <t>111,087,535</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,772,983</t>
+          <t>235,339,462</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>235,339,462</t>
+          <t>1,772,983</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
